--- a/5/search/FY4_Missile1_results/fine_tuned/original_top5_solutions.xlsx
+++ b/5/search/FY4_Missile1_results/fine_tuned/original_top5_solutions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,37 +487,177 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>315</v>
+        <v>265.5</v>
       </c>
       <c r="B2" t="n">
-        <v>128.8</v>
+        <v>122</v>
       </c>
       <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
         <v>12</v>
       </c>
-      <c r="D2" t="n">
-        <v>10</v>
-      </c>
       <c r="E2" t="n">
-        <v>12092.90424100193</v>
+        <v>10961.71196128481</v>
       </c>
       <c r="F2" t="n">
-        <v>907.0957589980717</v>
+        <v>1513.504341138233</v>
       </c>
       <c r="G2" t="n">
         <v>1800</v>
       </c>
       <c r="H2" t="n">
-        <v>13003.6577751702</v>
+        <v>10846.84784513925</v>
       </c>
       <c r="I2" t="n">
-        <v>-3.65777517020183</v>
+        <v>54.01736455293417</v>
       </c>
       <c r="J2" t="n">
-        <v>1310</v>
+        <v>1094.4</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>216</v>
+      </c>
+      <c r="B3" t="n">
+        <v>112</v>
+      </c>
+      <c r="C3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D3" t="n">
+        <v>14</v>
+      </c>
+      <c r="E3" t="n">
+        <v>9550.241546080095</v>
+      </c>
+      <c r="F3" t="n">
+        <v>946.6888278918884</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8281.702898900177</v>
+      </c>
+      <c r="I3" t="n">
+        <v>25.04155229729076</v>
+      </c>
+      <c r="J3" t="n">
+        <v>839.5999999999999</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>261</v>
+      </c>
+      <c r="B4" t="n">
+        <v>124</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10922.40850534004</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1510.106583064812</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H4" t="n">
+        <v>10689.63402136018</v>
+      </c>
+      <c r="I4" t="n">
+        <v>40.42633225924692</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1094.4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>229.5</v>
+      </c>
+      <c r="B5" t="n">
+        <v>124</v>
+      </c>
+      <c r="C5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>13</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10355.74753605646</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1245.677282124769</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H5" t="n">
+        <v>9308.837282148203</v>
+      </c>
+      <c r="I5" t="n">
+        <v>19.90286557751892</v>
+      </c>
+      <c r="J5" t="n">
+        <v>971.9</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>261</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D6" t="n">
+        <v>12</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10874.85242796781</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1209.84932752389</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H6" t="n">
+        <v>10687.13106991954</v>
+      </c>
+      <c r="I6" t="n">
+        <v>24.62331880972465</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1094.4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
